--- a/基本設計/15_DB基本設計書.xlsx
+++ b/基本設計/15_DB基本設計書.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R0db5fcacb7ce43f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rcd9b59b95a7b4fd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Table一覧" sheetId="3" r:id="R8a99dfc69adc41db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_全体ER図" sheetId="4" r:id="R6a81f048d4fe4b28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_ユーザー・組織" sheetId="5" r:id="Rc920c494cefb41b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_プロジェクト・タスク" sheetId="6" r:id="Rf222a0b499aa446d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_日報・通知・ログ" sheetId="7" r:id="R2f96fd73cda348fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Column定義" sheetId="8" r:id="R6b4a0135c9ab4c32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_FK・Constraint" sheetId="9" r:id="Rdd5da5f06b4541b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Index" sheetId="10" r:id="Rf4945f8e0f9f4717"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_LogicalDelete" sheetId="11" r:id="R6ae6fc06f96d48d4"/>
-  </x:sheets>
-</x:workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheets>
+    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="R958bf8c74a634fb2"/>
+    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="Rb09ef9c8cfb84a81"/>
+    <ns0:sheet name="02_Table一覧" sheetId="3" ns1:id="R3c2d46b5553c44e7"/>
+    <ns0:sheet name="03_全体ER図" sheetId="4" ns1:id="R0d9a7c5306274619"/>
+    <ns0:sheet name="04_ユーザー・組織" sheetId="5" ns1:id="R5e1e13cc9986490c"/>
+    <ns0:sheet name="05_プロジェクト・タスク" sheetId="6" ns1:id="Rf59bd5f2be2b4576"/>
+    <ns0:sheet name="06_日報・通知・ログ" sheetId="7" ns1:id="R5c01bd4bd7404044"/>
+    <ns0:sheet name="07_Column定義" sheetId="8" ns1:id="R8386718c95ac4f32"/>
+    <ns0:sheet name="08_FK・Constraint" sheetId="9" ns1:id="Rf27fa08505e44f0c"/>
+    <ns0:sheet name="09_Index" sheetId="10" ns1:id="Ra9bebf29050a43b7"/>
+    <ns0:sheet name="10_LogicalDelete" sheetId="11" ns1:id="Ra488a157440848ce"/>
+  </ns0:sheets>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23,7 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="7">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -60,8 +60,13 @@
       <x:sz val="10"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF172B40"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -88,8 +93,13 @@
         <x:fgColor rgb="FFE5EFF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF1F8"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -105,11 +115,25 @@
         <x:color rgb="FFD4DEE8"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -165,6 +189,21 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -432,7 +471,7 @@
         <x:v>Document Version</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="36" customHeight="1">
@@ -448,7 +487,7 @@
         <x:v>状態</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
-        <x:v>Review中</x:v>
+        <x:v>修正済</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="36" customHeight="1">
@@ -456,7 +495,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1213,7 +1252,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="3" t="str">
-        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+        <x:v>版数：Ver.2.6    改訂日：2026-09-29    基準Baseline：BL-2026-09-24</x:v>
       </x:c>
       <x:c r="B4" s="3"/>
       <x:c r="C4" s="3"/>
@@ -1304,16 +1343,34 @@
         <x:v>15_DB基本設計書</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="42" customHeight="1">
-      <x:c r="A9"/>
-      <x:c r="B9"/>
-      <x:c r="C9"/>
-      <x:c r="D9"/>
-      <x:c r="E9"/>
-      <x:c r="F9"/>
-      <x:c r="G9"/>
-      <x:c r="H9"/>
-      <x:c r="I9"/>
+    <x:row r="9" ht="65" customHeight="1">
+      <x:c r="A9" s="24" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B9" s="24" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="C9" s="24" t="str">
+        <x:v>CHG-DB-20260929-01：物理外鍵を非採用。論理参照・アプリ参照検証・明示関連削除へ統一。</x:v>
+      </x:c>
+      <x:c r="D9" s="24" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="E9" s="24" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F9" s="24" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G9" s="24" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H9" s="24" t="str">
+        <x:v>変更指示反映。正式承認は別途。</x:v>
+      </x:c>
+      <x:c r="I9" s="24" t="str">
+        <x:v>15_DB基本設計書</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="57" customHeight="1">
       <x:c r="A10"/>
@@ -2742,9 +2799,9 @@
       <x:c r="H22" s="12"/>
       <x:c r="I22" s="12"/>
     </x:row>
-    <x:row r="23" ht="32" customHeight="1">
+    <x:row r="23" ht="45" customHeight="1">
       <x:c r="A23" s="12" t="str">
-        <x:v>関係概略。FK項目・整合性は下表および08_FK・Constraint。</x:v>
+        <x:v>論理ER。物理外鍵は非採用。関連Columnと参照先は下表／07を参照。整合性方針の正本は08。</x:v>
       </x:c>
       <x:c r="B23" s="12"/>
       <x:c r="C23" s="12"/>
@@ -2846,7 +2903,7 @@
         <x:v>子Table</x:v>
       </x:c>
       <x:c r="E31" s="17" t="str">
-        <x:v>FK/中間Table</x:v>
+        <x:v>参照Column/中間Table</x:v>
       </x:c>
       <x:c r="F31" s="17" t="str">
         <x:v>関係</x:v>
@@ -3259,7 +3316,7 @@
       <x:c r="H47" s="7" t="str"/>
       <x:c r="I47" s="7"/>
     </x:row>
-    <x:row r="48" ht="36" customHeight="1">
+    <x:row r="48" ht="85" customHeight="1">
       <x:c r="A48" s="8" t="n">
         <x:v>17</x:v>
       </x:c>
@@ -3279,7 +3336,7 @@
         <x:v>Task Tag</x:v>
       </x:c>
       <x:c r="G48" s="8" t="str">
-        <x:v>Task削除時CASCADE</x:v>
+        <x:v>許可されたTask物理削除時のみ、task_tagsを先に同一Transactionで明示削除。DB自動連鎖なし。論理削除・取消では消さない。</x:v>
       </x:c>
       <x:c r="H48" s="8" t="str">
         <x:v>UNIQUE(task_id,tag)</x:v>
@@ -4050,7 +4107,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
-        <x:v>FK/UK</x:v>
+        <x:v>論理参照/UK</x:v>
       </x:c>
       <x:c r="H11" s="7" t="str">
         <x:v>employees.id</x:v>
@@ -4542,7 +4599,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G31" s="7" t="str">
-        <x:v>FK/UK</x:v>
+        <x:v>論理参照/UK</x:v>
       </x:c>
       <x:c r="H31" s="7" t="str">
         <x:v>users.id</x:v>
@@ -4568,7 +4625,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G32" s="8" t="str">
-        <x:v>FK/UK</x:v>
+        <x:v>論理参照/UK</x:v>
       </x:c>
       <x:c r="H32" s="8" t="str">
         <x:v>roles.id</x:v>
@@ -4618,7 +4675,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G34" s="8" t="str">
-        <x:v>FK/UK</x:v>
+        <x:v>論理参照/UK</x:v>
       </x:c>
       <x:c r="H34" s="8" t="str">
         <x:v>roles.id</x:v>
@@ -4644,7 +4701,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G35" s="7" t="str">
-        <x:v>FK/UK</x:v>
+        <x:v>論理参照/UK</x:v>
       </x:c>
       <x:c r="H35" s="7" t="str">
         <x:v>permissions.id</x:v>
@@ -4810,7 +4867,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G42" s="8" t="str">
-        <x:v>FK/IDX</x:v>
+        <x:v>論理参照/IDX</x:v>
       </x:c>
       <x:c r="H42" s="8" t="str"/>
     </x:row>
@@ -4856,7 +4913,7 @@
       </x:c>
       <x:c r="F44" s="8" t="str"/>
       <x:c r="G44" s="8" t="str">
-        <x:v>FK</x:v>
+        <x:v>論理参照</x:v>
       </x:c>
       <x:c r="H44" s="8" t="str">
         <x:v>employees.id</x:v>
@@ -5190,7 +5247,7 @@
       </x:c>
       <x:c r="F58" s="8" t="str"/>
       <x:c r="G58" s="8" t="str">
-        <x:v>FK</x:v>
+        <x:v>論理参照</x:v>
       </x:c>
       <x:c r="H58" s="8" t="str">
         <x:v>self</x:v>
@@ -5214,7 +5271,7 @@
       </x:c>
       <x:c r="F59" s="7" t="str"/>
       <x:c r="G59" s="7" t="str">
-        <x:v>FK</x:v>
+        <x:v>論理参照</x:v>
       </x:c>
       <x:c r="H59" s="7" t="str">
         <x:v>employees.id</x:v>
@@ -5558,7 +5615,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G73" s="7" t="str">
-        <x:v>FK/IDX</x:v>
+        <x:v>論理参照/IDX</x:v>
       </x:c>
       <x:c r="H73" s="7" t="str"/>
     </x:row>
@@ -5868,7 +5925,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G86" s="8" t="str">
-        <x:v>FK/UK</x:v>
+        <x:v>論理参照/UK</x:v>
       </x:c>
       <x:c r="H86" s="8" t="str"/>
     </x:row>
@@ -5892,7 +5949,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G87" s="7" t="str">
-        <x:v>FK/UK</x:v>
+        <x:v>論理参照/UK</x:v>
       </x:c>
       <x:c r="H87" s="7" t="str"/>
     </x:row>
@@ -6138,7 +6195,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G97" s="7" t="str">
-        <x:v>FK/IDX</x:v>
+        <x:v>論理参照/IDX</x:v>
       </x:c>
       <x:c r="H97" s="7" t="str"/>
     </x:row>
@@ -6160,7 +6217,7 @@
       </x:c>
       <x:c r="F98" s="8" t="str"/>
       <x:c r="G98" s="8" t="str">
-        <x:v>FK</x:v>
+        <x:v>論理参照</x:v>
       </x:c>
       <x:c r="H98" s="8" t="str">
         <x:v>self</x:v>
@@ -6230,7 +6287,7 @@
       </x:c>
       <x:c r="F101" s="7" t="str"/>
       <x:c r="G101" s="7" t="str">
-        <x:v>FK/IDX</x:v>
+        <x:v>論理参照/IDX</x:v>
       </x:c>
       <x:c r="H101" s="7" t="str"/>
     </x:row>
@@ -6254,7 +6311,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G102" s="8" t="str">
-        <x:v>FK</x:v>
+        <x:v>論理参照</x:v>
       </x:c>
       <x:c r="H102" s="8" t="str"/>
     </x:row>
@@ -6588,7 +6645,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G116" s="8" t="str">
-        <x:v>FK/IDX</x:v>
+        <x:v>論理参照/IDX</x:v>
       </x:c>
       <x:c r="H116" s="8" t="str"/>
     </x:row>
@@ -6612,7 +6669,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G117" s="7" t="str">
-        <x:v>FK</x:v>
+        <x:v>論理参照</x:v>
       </x:c>
       <x:c r="H117" s="7" t="str"/>
     </x:row>
@@ -6756,7 +6813,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G123" s="7" t="str">
-        <x:v>FK/IDX</x:v>
+        <x:v>論理参照/IDX</x:v>
       </x:c>
       <x:c r="H123" s="7" t="str"/>
     </x:row>
@@ -6904,7 +6961,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G129" s="7" t="str">
-        <x:v>FK</x:v>
+        <x:v>論理参照</x:v>
       </x:c>
       <x:c r="H129" s="7" t="str"/>
     </x:row>
@@ -6976,7 +7033,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G132" s="8" t="str">
-        <x:v>FK/IDX</x:v>
+        <x:v>論理参照/IDX</x:v>
       </x:c>
       <x:c r="H132" s="8" t="str"/>
     </x:row>
@@ -7068,7 +7125,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G136" s="8" t="str">
-        <x:v>FK</x:v>
+        <x:v>論理参照</x:v>
       </x:c>
       <x:c r="H136" s="8" t="str"/>
     </x:row>
@@ -7244,7 +7301,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G143" s="7" t="str">
-        <x:v>FK/IDX</x:v>
+        <x:v>論理参照/IDX</x:v>
       </x:c>
       <x:c r="H143" s="7" t="str">
         <x:v>tasks.id</x:v>
@@ -7370,7 +7427,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G148" s="8" t="str">
-        <x:v>FK/UK</x:v>
+        <x:v>論理参照/UK</x:v>
       </x:c>
       <x:c r="H148" s="8" t="str"/>
     </x:row>
@@ -7394,7 +7451,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G149" s="7" t="str">
-        <x:v>FK/UK/IDX</x:v>
+        <x:v>論理参照/UK/IDX</x:v>
       </x:c>
       <x:c r="H149" s="7" t="str"/>
     </x:row>
@@ -7658,7 +7715,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G160" s="8" t="str">
-        <x:v>FK/UK</x:v>
+        <x:v>論理参照/UK</x:v>
       </x:c>
       <x:c r="H160" s="8" t="str"/>
     </x:row>
@@ -7682,7 +7739,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G161" s="7" t="str">
-        <x:v>FK/UK</x:v>
+        <x:v>論理参照/UK</x:v>
       </x:c>
       <x:c r="H161" s="7" t="str"/>
     </x:row>
@@ -7730,7 +7787,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G163" s="7" t="str">
-        <x:v>FK/IDX</x:v>
+        <x:v>論理参照/IDX</x:v>
       </x:c>
       <x:c r="H163" s="7" t="str"/>
     </x:row>
@@ -7991,7 +8048,7 @@
       </x:c>
       <x:c r="F174" s="8" t="str"/>
       <x:c r="G174" s="8" t="str">
-        <x:v>FK/IDX</x:v>
+        <x:v>論理参照/IDX</x:v>
       </x:c>
       <x:c r="H174" s="8" t="str"/>
     </x:row>
@@ -8425,7 +8482,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="G192" s="8" t="str">
-        <x:v>FK/IDX</x:v>
+        <x:v>論理参照/IDX</x:v>
       </x:c>
       <x:c r="H192" s="8" t="str"/>
     </x:row>
@@ -8543,7 +8600,7 @@
       </x:c>
       <x:c r="F197" s="7" t="str"/>
       <x:c r="G197" s="7" t="str">
-        <x:v>FK/IDX</x:v>
+        <x:v>論理参照/IDX</x:v>
       </x:c>
       <x:c r="H197" s="7" t="str">
         <x:v>存在しないも記録</x:v>
@@ -9035,7 +9092,7 @@
       </x:c>
       <x:c r="H8" s="8" t="str"/>
     </x:row>
-    <x:row r="9" ht="36" customHeight="1">
+    <x:row r="9" ht="65" customHeight="1">
       <x:c r="A9" s="7" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -9043,7 +9100,7 @@
         <x:v>users</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
-        <x:v>UNIQUE/FK</x:v>
+        <x:v>UNIQUE/論理参照</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
         <x:v>employee_id</x:v>
@@ -9057,7 +9114,9 @@
       <x:c r="G9" s="7" t="str">
         <x:v>社員物理削除不可</x:v>
       </x:c>
-      <x:c r="H9" s="7" t="str"/>
+      <x:c r="H9" s="7" t="str">
+        <x:v>employee_idのUNIQUEはDBで維持。社員存在・削除可否はAPIが検証。</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="36" customHeight="1">
       <x:c r="A10" s="8" t="n">
@@ -9307,7 +9366,7 @@
         <x:v>更新時version+1</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="36" customHeight="1">
+    <x:row r="20" ht="100" customHeight="1">
       <x:c r="A20" s="8" t="n">
         <x:v>20</x:v>
       </x:c>
@@ -9330,7 +9389,7 @@
         <x:v>UNIQUE(task_id,tag)</x:v>
       </x:c>
       <x:c r="H20" s="8" t="str">
-        <x:v>Task削除時CASCADE</x:v>
+        <x:v>許可されたTask物理削除時のみ、task_tagsを先に同一Transactionで明示削除。DB自動連鎖なし。論理削除・取消では消さない。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="72" customHeight="1">
@@ -9487,6 +9546,58 @@
       </x:c>
       <x:c r="H26" s="19" t="str">
         <x:v>Log結果Codeの保存制約。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="170" customHeight="1">
+      <x:c r="A28" s="25" t="str">
+        <x:v>方針</x:v>
+      </x:c>
+      <x:c r="B28" s="25" t="str">
+        <x:v>全Table</x:v>
+      </x:c>
+      <x:c r="C28" s="25" t="str">
+        <x:v>物理外鍵なし</x:v>
+      </x:c>
+      <x:c r="D28" s="25" t="str">
+        <x:v>DB-REF-001</x:v>
+      </x:c>
+      <x:c r="E28" s="25" t="str">
+        <x:v>全Tableで物理外鍵制約を作成しない。参照Column・ER関係は論理参照として保持する。PK/UNIQUE/NOT NULL/CHECK/Indexは維持。参照整合性は書込API・Batchが同一Transaction内で検証し、17／30の排他方針に従う。DBの外鍵例外や自動連鎖削除に依存しない。</x:v>
+      </x:c>
+      <x:c r="F28" s="25" t="str">
+        <x:v>既存API Error定義参照</x:v>
+      </x:c>
+      <x:c r="G28" s="25" t="str">
+        <x:v>親のPK変更・参照残存時の物理削除は原則不可</x:v>
+      </x:c>
+      <x:c r="H28" s="25" t="str">
+        <x:v>Sheet名は既存参照互換のため維持。「論理参照」は物理制約ではない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="125" customHeight="1">
+      <x:c r="A29" s="24" t="str">
+        <x:v>検証</x:v>
+      </x:c>
+      <x:c r="B29" s="24" t="str">
+        <x:v>API/Batch</x:v>
+      </x:c>
+      <x:c r="C29" s="24" t="str">
+        <x:v>論理参照</x:v>
+      </x:c>
+      <x:c r="D29" s="24" t="str">
+        <x:v>DB-REF-002</x:v>
+      </x:c>
+      <x:c r="E29" s="24" t="str">
+        <x:v>業務入力の参照IDは存在・未削除・必要状態を検証。Null可はNull時のみ対象外。履歴保存後に親停止を理由に履歴を削除しない。</x:v>
+      </x:c>
+      <x:c r="F29" s="24" t="str">
+        <x:v>各APIの既定Code</x:v>
+      </x:c>
+      <x:c r="G29" s="24" t="str">
+        <x:v>削除前に関連行を再確認。明示削除の許可範囲は既存業務仕様どおり。</x:v>
+      </x:c>
+      <x:c r="H29" s="24" t="str">
+        <x:v>失敗時は全体Rollback。直接SQLでの業務更新は禁止し、運用投入も同じ検証を実施。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/基本設計/15_DB基本設計書.xlsx
+++ b/基本設計/15_DB基本設計書.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <ns0:sheets>
-    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="R958bf8c74a634fb2"/>
-    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="Rb09ef9c8cfb84a81"/>
-    <ns0:sheet name="02_Table一覧" sheetId="3" ns1:id="R3c2d46b5553c44e7"/>
-    <ns0:sheet name="03_全体ER図" sheetId="4" ns1:id="R0d9a7c5306274619"/>
-    <ns0:sheet name="04_ユーザー・組織" sheetId="5" ns1:id="R5e1e13cc9986490c"/>
-    <ns0:sheet name="05_プロジェクト・タスク" sheetId="6" ns1:id="Rf59bd5f2be2b4576"/>
-    <ns0:sheet name="06_日報・通知・ログ" sheetId="7" ns1:id="R5c01bd4bd7404044"/>
-    <ns0:sheet name="07_Column定義" sheetId="8" ns1:id="R8386718c95ac4f32"/>
-    <ns0:sheet name="08_FK・Constraint" sheetId="9" ns1:id="Rf27fa08505e44f0c"/>
-    <ns0:sheet name="09_Index" sheetId="10" ns1:id="Ra9bebf29050a43b7"/>
-    <ns0:sheet name="10_LogicalDelete" sheetId="11" ns1:id="Ra488a157440848ce"/>
-  </ns0:sheets>
-</ns0:workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rc5a9411a952f4e1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rd9a2eaf709ab419c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Table一覧" sheetId="3" r:id="R93adf5b20420427d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_全体ER図" sheetId="4" r:id="Ree617b7ed3ee4cf8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_ユーザー・組織" sheetId="5" r:id="R9b6a335d7aa747bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_プロジェクト・タスク" sheetId="6" r:id="R7764bbcb032a4799"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_日報・通知・ログ" sheetId="7" r:id="Rcd433949e70f4933"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Column定義" sheetId="8" r:id="R158259d2941540ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_論理参照・制約" sheetId="9" r:id="R1a2c36c7cc644179"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Index" sheetId="10" r:id="R622c7152d4a843a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_LogicalDelete" sheetId="11" r:id="Rad601c0349d84949"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23,7 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -65,8 +65,13 @@
       <x:color rgb="FF172B40"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF222222"/>
+      <x:name val="Meiryo"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -98,8 +103,13 @@
         <x:fgColor rgb="FFEAF1F8"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="4">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -129,11 +139,25 @@
         <x:color rgb="FFD9E2EC"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -205,6 +229,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -471,7 +507,7 @@
         <x:v>Document Version</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.9</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="36" customHeight="1">
@@ -495,7 +531,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1252,7 +1288,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="3" t="str">
-        <x:v>版数：Ver.2.6    改訂日：2026-09-29    基準Baseline：BL-2026-09-24</x:v>
+        <x:v>版数：Ver.2.9    改訂日：2026-10-08    基準Baseline：BL-2026-09-24</x:v>
       </x:c>
       <x:c r="B4" s="3"/>
       <x:c r="C4" s="3"/>
@@ -1372,37 +1408,85 @@
         <x:v>15_DB基本設計書</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="57" customHeight="1">
-      <x:c r="A10"/>
-      <x:c r="B10"/>
-      <x:c r="C10"/>
-      <x:c r="D10"/>
-      <x:c r="E10"/>
-      <x:c r="F10"/>
-      <x:c r="G10"/>
-      <x:c r="H10"/>
+    <x:row r="10" ht="100" customHeight="1">
+      <x:c r="A10" s="30" t="str">
+        <x:v>Ver.2.7</x:v>
+      </x:c>
+      <x:c r="B10" s="30" t="str">
+        <x:v>2026-09-30</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="str">
+        <x:v>CHG-BATCH-20260930-01：BATCH-001実行/Timeout/監視/Retryとnotifications.id Identityを確定。関連文書を同期。</x:v>
+      </x:c>
+      <x:c r="D10" s="30" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H10" s="30" t="str">
+        <x:v>Review修正指示反映。基準Baselineは維持、正式承認は別途。</x:v>
+      </x:c>
       <x:c r="I10"/>
     </x:row>
-    <x:row r="11" ht="57" customHeight="1">
-      <x:c r="A11"/>
-      <x:c r="B11"/>
-      <x:c r="C11"/>
-      <x:c r="D11"/>
-      <x:c r="E11"/>
-      <x:c r="F11"/>
-      <x:c r="G11"/>
-      <x:c r="H11"/>
+    <x:row r="11" ht="34" customHeight="1">
+      <x:c r="A11" s="21" t="str">
+        <x:v>Ver.2.8</x:v>
+      </x:c>
+      <x:c r="B11" s="21" t="str">
+        <x:v>2026-10-07</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="str">
+        <x:v>CHG-ACTOR-20261007-01：Task報告者・Comment投稿者・添付登録者・Task変更操作者の論理参照先と設定元を確定。</x:v>
+      </x:c>
+      <x:c r="D11" s="21" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="E11" s="21" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F11" s="21" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G11" s="21" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H11" s="21" t="str">
+        <x:v>基本設計基線補完。正式承認は別途。</x:v>
+      </x:c>
       <x:c r="I11"/>
     </x:row>
-    <x:row r="12" ht="72" customHeight="1">
-      <x:c r="A12"/>
-      <x:c r="B12"/>
-      <x:c r="C12"/>
-      <x:c r="D12"/>
-      <x:c r="E12"/>
-      <x:c r="F12"/>
-      <x:c r="G12"/>
-      <x:c r="H12"/>
+    <x:row r="12" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A12" s="21" t="str">
+        <x:v>Ver.2.9</x:v>
+      </x:c>
+      <x:c r="B12" s="21" t="str">
+        <x:v>2026-10-08</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="str">
+        <x:v>CHG-NTF-20261008-01：notifications.related_typeをTASK／PROJECT／SYSTEMへ統一し、related_idの対応を確定。</x:v>
+      </x:c>
+      <x:c r="D12" s="21" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E12" s="21" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F12" s="21" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G12" s="21" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H12" s="21" t="str">
+        <x:v>API・業務Rule・Batchとの対応を同期。基準Baselineは維持。</x:v>
+      </x:c>
       <x:c r="I12"/>
     </x:row>
     <x:row r="13" ht="72" customHeight="1">
@@ -3370,6 +3454,110 @@
       </x:c>
       <x:c r="I49" s="7"/>
     </x:row>
+    <x:row r="50" ht="34" customHeight="1">
+      <x:c r="A50" s="31" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B50" s="31" t="str">
+        <x:v>employees</x:v>
+      </x:c>
+      <x:c r="C50" s="31" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="D50" s="31" t="str">
+        <x:v>tasks</x:v>
+      </x:c>
+      <x:c r="E50" s="31" t="str">
+        <x:v>tasks.reporter_id</x:v>
+      </x:c>
+      <x:c r="F50" s="31" t="str">
+        <x:v>Task報告者</x:v>
+      </x:c>
+      <x:c r="G50" s="31" t="str">
+        <x:v>登録時の認証Userに紐づく社員</x:v>
+      </x:c>
+      <x:c r="H50" s="31" t="str">
+        <x:v>employees.idへの論理参照</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="34" customHeight="1">
+      <x:c r="A51" s="31" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B51" s="31" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C51" s="31" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="D51" s="31" t="str">
+        <x:v>task_comments</x:v>
+      </x:c>
+      <x:c r="E51" s="31" t="str">
+        <x:v>task_comments.user_id</x:v>
+      </x:c>
+      <x:c r="F51" s="31" t="str">
+        <x:v>Comment投稿者</x:v>
+      </x:c>
+      <x:c r="G51" s="31" t="str">
+        <x:v>認証UserをServer設定</x:v>
+      </x:c>
+      <x:c r="H51" s="31" t="str">
+        <x:v>停止後も履歴保持</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="34" customHeight="1">
+      <x:c r="A52" s="31" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B52" s="31" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C52" s="31" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="D52" s="31" t="str">
+        <x:v>task_attachments</x:v>
+      </x:c>
+      <x:c r="E52" s="31" t="str">
+        <x:v>task_attachments.uploaded_by</x:v>
+      </x:c>
+      <x:c r="F52" s="31" t="str">
+        <x:v>添付登録者</x:v>
+      </x:c>
+      <x:c r="G52" s="31" t="str">
+        <x:v>認証UserをServer設定</x:v>
+      </x:c>
+      <x:c r="H52" s="31" t="str">
+        <x:v>停止後も履歴保持</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="34" customHeight="1">
+      <x:c r="A53" s="31" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B53" s="31" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C53" s="31" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="D53" s="31" t="str">
+        <x:v>task_histories</x:v>
+      </x:c>
+      <x:c r="E53" s="31" t="str">
+        <x:v>task_histories.changed_by</x:v>
+      </x:c>
+      <x:c r="F53" s="31" t="str">
+        <x:v>Task変更操作者</x:v>
+      </x:c>
+      <x:c r="G53" s="31" t="str">
+        <x:v>認証UserをServer設定</x:v>
+      </x:c>
+      <x:c r="H53" s="31" t="str">
+        <x:v>物理削除不可</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:I1"/>
@@ -3455,7 +3643,7 @@
         <x:v>07_Column定義 / Table=users</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
         <x:v>09_Index</x:v>
@@ -3469,7 +3657,7 @@
         <x:v>07_Column定義 / Table=roles</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
         <x:v>09_Index</x:v>
@@ -3483,7 +3671,7 @@
         <x:v>07_Column定義 / Table=permissions</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
         <x:v>09_Index</x:v>
@@ -3497,7 +3685,7 @@
         <x:v>07_Column定義 / Table=user_roles</x:v>
       </x:c>
       <x:c r="C11" s="7" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
         <x:v>09_Index</x:v>
@@ -3511,7 +3699,7 @@
         <x:v>07_Column定義 / Table=role_permissions</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
         <x:v>09_Index</x:v>
@@ -3525,7 +3713,7 @@
         <x:v>07_Column定義 / Table=employees</x:v>
       </x:c>
       <x:c r="C13" s="7" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D13" s="7" t="str">
         <x:v>09_Index</x:v>
@@ -3539,7 +3727,7 @@
         <x:v>07_Column定義 / Table=departments</x:v>
       </x:c>
       <x:c r="C14" s="8" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D14" s="8" t="str">
         <x:v>09_Index</x:v>
@@ -3629,7 +3817,7 @@
         <x:v>07_Column定義 / Table=projects</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
         <x:v>09_Index</x:v>
@@ -3643,7 +3831,7 @@
         <x:v>07_Column定義 / Table=project_members</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
         <x:v>09_Index</x:v>
@@ -3657,7 +3845,7 @@
         <x:v>07_Column定義 / Table=tasks</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
         <x:v>09_Index</x:v>
@@ -3671,7 +3859,7 @@
         <x:v>07_Column定義 / Table=task_comments</x:v>
       </x:c>
       <x:c r="C11" s="7" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
         <x:v>09_Index</x:v>
@@ -3685,7 +3873,7 @@
         <x:v>07_Column定義 / Table=task_attachments</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
         <x:v>09_Index</x:v>
@@ -3699,7 +3887,7 @@
         <x:v>07_Column定義 / Table=task_histories</x:v>
       </x:c>
       <x:c r="C13" s="7" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D13" s="7" t="str">
         <x:v>09_Index</x:v>
@@ -3713,7 +3901,7 @@
         <x:v>07_Column定義 / Table=task_tags</x:v>
       </x:c>
       <x:c r="C14" s="8" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D14" s="8" t="str">
         <x:v>09_Index</x:v>
@@ -3803,7 +3991,7 @@
         <x:v>07_Column定義 / Table=daily_reports</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
         <x:v>09_Index</x:v>
@@ -3817,7 +4005,7 @@
         <x:v>07_Column定義 / Table=daily_report_tasks</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
         <x:v>09_Index</x:v>
@@ -3831,7 +4019,7 @@
         <x:v>07_Column定義 / Table=notifications</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
         <x:v>09_Index</x:v>
@@ -3845,7 +4033,7 @@
         <x:v>07_Column定義 / Table=operation_logs</x:v>
       </x:c>
       <x:c r="C11" s="7" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
         <x:v>09_Index</x:v>
@@ -3859,7 +4047,7 @@
         <x:v>07_Column定義 / Table=refresh_tokens</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
         <x:v>09_Index</x:v>
@@ -3873,7 +4061,7 @@
         <x:v>07_Column定義 / Table=login_histories</x:v>
       </x:c>
       <x:c r="C13" s="7" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D13" s="7" t="str">
         <x:v>09_Index</x:v>
@@ -3887,7 +4075,7 @@
         <x:v>07_Column定義 / Table=business_holidays</x:v>
       </x:c>
       <x:c r="C14" s="8" t="str">
-        <x:v>03_全体ER図・08_FK・Constraint</x:v>
+        <x:v>03_全体ER図・08_論理参照・制約</x:v>
       </x:c>
       <x:c r="D14" s="8" t="str">
         <x:v>09_Index</x:v>
@@ -6291,7 +6479,7 @@
       </x:c>
       <x:c r="H101" s="7" t="str"/>
     </x:row>
-    <x:row r="102" ht="36" customHeight="1">
+    <x:row r="102" ht="44" customHeight="1">
       <x:c r="A102" s="8" t="str">
         <x:v>tasks</x:v>
       </x:c>
@@ -6313,7 +6501,9 @@
       <x:c r="G102" s="8" t="str">
         <x:v>論理参照</x:v>
       </x:c>
-      <x:c r="H102" s="8" t="str"/>
+      <x:c r="H102" s="8" t="str">
+        <x:v>employees.id。Task登録時に認証Userのusers.employee_idをServer設定。Client指定不可、登録後変更不可。</x:v>
+      </x:c>
     </x:row>
     <x:row r="103" ht="57" customHeight="1">
       <x:c r="A103" s="7" t="str">
@@ -6649,7 +6839,7 @@
       </x:c>
       <x:c r="H116" s="8" t="str"/>
     </x:row>
-    <x:row r="117" ht="36" customHeight="1">
+    <x:row r="117" ht="50" customHeight="1">
       <x:c r="A117" s="7" t="str">
         <x:v>task_comments</x:v>
       </x:c>
@@ -6671,7 +6861,9 @@
       <x:c r="G117" s="7" t="str">
         <x:v>論理参照</x:v>
       </x:c>
-      <x:c r="H117" s="7" t="str"/>
+      <x:c r="H117" s="7" t="str">
+        <x:v>users.id。Comment登録時に認証Userのusers.idをServer設定。Client指定不可。表示名はusers.employee_id→employees.id→employees.name。</x:v>
+      </x:c>
     </x:row>
     <x:row r="118" ht="36" customHeight="1">
       <x:c r="A118" s="8" t="str">
@@ -6941,7 +7133,7 @@
       </x:c>
       <x:c r="H128" s="8" t="str"/>
     </x:row>
-    <x:row r="129" ht="36" customHeight="1">
+    <x:row r="129" ht="44" customHeight="1">
       <x:c r="A129" s="7" t="str">
         <x:v>task_attachments</x:v>
       </x:c>
@@ -6963,7 +7155,9 @@
       <x:c r="G129" s="7" t="str">
         <x:v>論理参照</x:v>
       </x:c>
-      <x:c r="H129" s="7" t="str"/>
+      <x:c r="H129" s="7" t="str">
+        <x:v>users.id。添付登録時に認証Userのusers.idをServer設定。Client指定不可。</x:v>
+      </x:c>
     </x:row>
     <x:row r="130" ht="42" customHeight="1">
       <x:c r="A130" s="8" t="str">
@@ -7105,7 +7299,7 @@
       </x:c>
       <x:c r="H135" s="7" t="str"/>
     </x:row>
-    <x:row r="136" ht="36" customHeight="1">
+    <x:row r="136" ht="44" customHeight="1">
       <x:c r="A136" s="8" t="str">
         <x:v>task_histories</x:v>
       </x:c>
@@ -7127,7 +7321,9 @@
       <x:c r="G136" s="8" t="str">
         <x:v>論理参照</x:v>
       </x:c>
-      <x:c r="H136" s="8" t="str"/>
+      <x:c r="H136" s="8" t="str">
+        <x:v>users.id。Task変更処理で認証Userのusers.idをServer設定。Client指定不可。</x:v>
+      </x:c>
     </x:row>
     <x:row r="137" ht="42" customHeight="1">
       <x:c r="A137" s="7" t="str">
@@ -7743,7 +7939,7 @@
       </x:c>
       <x:c r="H161" s="7" t="str"/>
     </x:row>
-    <x:row r="162" ht="36" customHeight="1">
+    <x:row r="162" ht="140" customHeight="1">
       <x:c r="A162" s="8" t="str">
         <x:v>notifications</x:v>
       </x:c>
@@ -7765,7 +7961,9 @@
       <x:c r="G162" s="8" t="str">
         <x:v>PK</x:v>
       </x:c>
-      <x:c r="H162" s="8" t="str"/>
+      <x:c r="H162" s="8" t="str">
+        <x:v>採番方式：Identity。BIGINT GENERATED BY DEFAULT AS IDENTITY PRIMARY KEY。INSERTはid省略でDB採番。欠番許容。ApplicationによるMAX(id)+1等は使用しない。</x:v>
+      </x:c>
     </x:row>
     <x:row r="163" ht="36" customHeight="1">
       <x:c r="A163" s="7" t="str">
@@ -7866,7 +8064,7 @@
       </x:c>
       <x:c r="H166" s="8" t="str"/>
     </x:row>
-    <x:row r="167" ht="36" customHeight="1">
+    <x:row r="167" ht="72" hidden="0" customHeight="1">
       <x:c r="A167" s="7" t="str">
         <x:v>notifications</x:v>
       </x:c>
@@ -7886,7 +8084,9 @@
       <x:c r="G167" s="7" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="H167" s="7" t="str"/>
+      <x:c r="H167" s="7" t="str">
+        <x:v>TASK/PROJECT/SYSTEM。TASKはtaskId、PROJECTはprojectId、SYSTEMはrelated_id=NULL。組合せは16／28 BR-NTF-003、20／37_バッチを正本とする。</x:v>
+      </x:c>
     </x:row>
     <x:row r="168" ht="36" customHeight="1">
       <x:c r="A168" s="8" t="str">
@@ -8309,7 +8509,7 @@
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="H185" s="7" t="str">
-        <x:v>SUCCESS/FAILURE。08_FK・ConstraintのCHECK参照。</x:v>
+        <x:v>SUCCESS/FAILURE。08_論理参照・制約のCHECK参照。</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="36" customHeight="1">
@@ -8653,7 +8853,7 @@
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="H199" s="7" t="str">
-        <x:v>SUCCESS/FAILURE。08_FK・ConstraintのCHECK参照。</x:v>
+        <x:v>SUCCESS/FAILURE。08_論理参照・制約のCHECK参照。</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="36" customHeight="1">
@@ -8978,7 +9178,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>08_FK・Constraint</x:v>
+        <x:v>08_論理参照・制約</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -9548,6 +9748,32 @@
         <x:v>Log結果Codeの保存制約。</x:v>
       </x:c>
     </x:row>
+    <x:row r="27" ht="60" customHeight="1">
+      <x:c r="A27" s="31" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B27" s="31" t="str">
+        <x:v>tasks/task_comments/task_attachments/task_histories</x:v>
+      </x:c>
+      <x:c r="C27" s="31" t="str">
+        <x:v>論理参照</x:v>
+      </x:c>
+      <x:c r="D27" s="31" t="str">
+        <x:v>reporter_id / user_id / uploaded_by / changed_by</x:v>
+      </x:c>
+      <x:c r="E27" s="31" t="str">
+        <x:v>報告者・操作者IDの意味統一</x:v>
+      </x:c>
+      <x:c r="F27" s="31" t="str">
+        <x:v>各APIの既定Code</x:v>
+      </x:c>
+      <x:c r="G27" s="31" t="str">
+        <x:v>親停止・論理削除後も履歴保持</x:v>
+      </x:c>
+      <x:c r="H27" s="31" t="str">
+        <x:v>tasks.reporter_id→employees.id。その他3項目→users.id。物理外鍵なし。設定元は13／22・23、17／29参照。</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" ht="170" customHeight="1">
       <x:c r="A28" s="25" t="str">
         <x:v>方針</x:v>
@@ -9602,9 +9828,9 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A3:H3"/>
     <x:mergeCell ref="A5:H5"/>
+    <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
